--- a/db/producto.xlsx
+++ b/db/producto.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -427,7 +427,7 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B2" t="str">
         <v>Pizza</v>
@@ -445,41 +445,15 @@
         <v>1</v>
       </c>
       <c r="G2" t="str">
-        <v>Pizza familiar</v>
+        <v>Pizza extra familiar</v>
       </c>
       <c r="H2" t="str">
-        <v>[{"Name": "Queso", "amount": "1"}, {"Name": "Jam\u00f3n", "amount": "2"}]</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Pizza</v>
-      </c>
-      <c r="C3" t="str">
-        <v>pizza.jpg</v>
-      </c>
-      <c r="D3">
-        <v>30000</v>
-      </c>
-      <c r="E3">
-        <v>25000</v>
-      </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Pizza familiar</v>
-      </c>
-      <c r="H3" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/db/producto.xlsx
+++ b/db/producto.xlsx
@@ -1,41 +1,80 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lyle\Pulloc\Project\gestor-restaurante\db\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C2DD5D-7BA0-4216-89DB-937772A30FA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="16">
+  <si>
+    <t>Uid</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Image</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Discount_price</t>
+  </si>
+  <si>
+    <t>IsActive</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Items</t>
+  </si>
+  <si>
+    <t>Pizza</t>
+  </si>
+  <si>
+    <t>pizza.jpg</t>
+  </si>
+  <si>
+    <t>Pizza extra familiar</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>hamburguesa</t>
+  </si>
+  <si>
+    <t>perro</t>
+  </si>
+  <si>
+    <t>hamburguesa.jpg</t>
+  </si>
+  <si>
+    <t>perro.jpg</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,6 +111,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,64 +443,2803 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H121"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Uid</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Name</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Image</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Price</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Discount_price</v>
-      </c>
-      <c r="F1" t="str">
-        <v>IsActive</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Items</v>
-      </c>
-    </row>
-    <row r="2">
+    <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>30000</v>
+      </c>
+      <c r="E2">
+        <v>25000</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B2" t="str">
-        <v>Pizza</v>
-      </c>
-      <c r="C2" t="str">
-        <v>pizza.jpg</v>
-      </c>
-      <c r="D2">
-        <v>30000</v>
-      </c>
-      <c r="E2">
-        <v>25000</v>
-      </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Pizza extra familiar</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3">
+        <v>10000</v>
+      </c>
+      <c r="E3">
+        <v>25000</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>15000</v>
+      </c>
+      <c r="E4">
+        <v>25000</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>30000</v>
+      </c>
+      <c r="E5">
+        <v>25000</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6">
+        <v>10000</v>
+      </c>
+      <c r="E6">
+        <v>25000</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>15000</v>
+      </c>
+      <c r="E7">
+        <v>25000</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8">
+        <v>30000</v>
+      </c>
+      <c r="E8">
+        <v>25000</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9">
+        <v>10000</v>
+      </c>
+      <c r="E9">
+        <v>25000</v>
+      </c>
+      <c r="F9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10">
+        <v>15000</v>
+      </c>
+      <c r="E10">
+        <v>25000</v>
+      </c>
+      <c r="F10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>30000</v>
+      </c>
+      <c r="E11">
+        <v>25000</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12">
+        <v>10000</v>
+      </c>
+      <c r="E12">
+        <v>25000</v>
+      </c>
+      <c r="F12" t="b">
+        <v>1</v>
+      </c>
+      <c r="G12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13">
+        <v>15000</v>
+      </c>
+      <c r="E13">
+        <v>25000</v>
+      </c>
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>30000</v>
+      </c>
+      <c r="E14">
+        <v>25000</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15">
+        <v>10000</v>
+      </c>
+      <c r="E15">
+        <v>25000</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D16">
+        <v>15000</v>
+      </c>
+      <c r="E16">
+        <v>25000</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>30000</v>
+      </c>
+      <c r="E17">
+        <v>25000</v>
+      </c>
+      <c r="F17" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D18">
+        <v>10000</v>
+      </c>
+      <c r="E18">
+        <v>25000</v>
+      </c>
+      <c r="F18" t="b">
+        <v>1</v>
+      </c>
+      <c r="G18" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19">
+        <v>15000</v>
+      </c>
+      <c r="E19">
+        <v>25000</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20">
+        <v>30000</v>
+      </c>
+      <c r="E20">
+        <v>25000</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" t="s">
+        <v>14</v>
+      </c>
+      <c r="D21">
+        <v>10000</v>
+      </c>
+      <c r="E21">
+        <v>25000</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22">
+        <v>15000</v>
+      </c>
+      <c r="E22">
+        <v>25000</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23">
+        <v>30000</v>
+      </c>
+      <c r="E23">
+        <v>25000</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>13</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D24">
+        <v>10000</v>
+      </c>
+      <c r="E24">
+        <v>25000</v>
+      </c>
+      <c r="F24" t="b">
+        <v>1</v>
+      </c>
+      <c r="G24" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25">
+        <v>15000</v>
+      </c>
+      <c r="E25">
+        <v>25000</v>
+      </c>
+      <c r="F25" t="b">
+        <v>1</v>
+      </c>
+      <c r="G25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26">
+        <v>30000</v>
+      </c>
+      <c r="E26">
+        <v>25000</v>
+      </c>
+      <c r="F26" t="b">
+        <v>1</v>
+      </c>
+      <c r="G26" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>14</v>
+      </c>
+      <c r="D27">
+        <v>10000</v>
+      </c>
+      <c r="E27">
+        <v>25000</v>
+      </c>
+      <c r="F27" t="b">
+        <v>1</v>
+      </c>
+      <c r="G27" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>15000</v>
+      </c>
+      <c r="E28">
+        <v>25000</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29">
+        <v>30000</v>
+      </c>
+      <c r="E29">
+        <v>25000</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" t="s">
+        <v>14</v>
+      </c>
+      <c r="D30">
+        <v>10000</v>
+      </c>
+      <c r="E30">
+        <v>25000</v>
+      </c>
+      <c r="F30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" t="s">
+        <v>15</v>
+      </c>
+      <c r="D31">
+        <v>15000</v>
+      </c>
+      <c r="E31">
+        <v>25000</v>
+      </c>
+      <c r="F31" t="b">
+        <v>1</v>
+      </c>
+      <c r="G31" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32">
+        <v>30000</v>
+      </c>
+      <c r="E32">
+        <v>25000</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>12</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="D33">
+        <v>10000</v>
+      </c>
+      <c r="E33">
+        <v>25000</v>
+      </c>
+      <c r="F33" t="b">
+        <v>1</v>
+      </c>
+      <c r="G33" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34">
+        <v>15000</v>
+      </c>
+      <c r="E34">
+        <v>25000</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35">
+        <v>30000</v>
+      </c>
+      <c r="E35">
+        <v>25000</v>
+      </c>
+      <c r="F35" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>12</v>
+      </c>
+      <c r="C36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36">
+        <v>10000</v>
+      </c>
+      <c r="E36">
+        <v>25000</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D37">
+        <v>15000</v>
+      </c>
+      <c r="E37">
+        <v>25000</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38">
+        <v>30000</v>
+      </c>
+      <c r="E38">
+        <v>25000</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+      <c r="D39">
+        <v>10000</v>
+      </c>
+      <c r="E39">
+        <v>25000</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D40">
+        <v>15000</v>
+      </c>
+      <c r="E40">
+        <v>25000</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41">
+        <v>30000</v>
+      </c>
+      <c r="E41">
+        <v>25000</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" t="s">
+        <v>14</v>
+      </c>
+      <c r="D42">
+        <v>10000</v>
+      </c>
+      <c r="E42">
+        <v>25000</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43">
+        <v>15000</v>
+      </c>
+      <c r="E43">
+        <v>25000</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44">
+        <v>30000</v>
+      </c>
+      <c r="E44">
+        <v>25000</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>12</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D45">
+        <v>10000</v>
+      </c>
+      <c r="E45">
+        <v>25000</v>
+      </c>
+      <c r="F45" t="b">
+        <v>1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>15000</v>
+      </c>
+      <c r="E46">
+        <v>25000</v>
+      </c>
+      <c r="F46" t="b">
+        <v>1</v>
+      </c>
+      <c r="G46" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47">
+        <v>30000</v>
+      </c>
+      <c r="E47">
+        <v>25000</v>
+      </c>
+      <c r="F47" t="b">
+        <v>1</v>
+      </c>
+      <c r="G47" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>14</v>
+      </c>
+      <c r="D48">
+        <v>10000</v>
+      </c>
+      <c r="E48">
+        <v>25000</v>
+      </c>
+      <c r="F48" t="b">
+        <v>1</v>
+      </c>
+      <c r="G48" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49">
+        <v>15000</v>
+      </c>
+      <c r="E49">
+        <v>25000</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50">
+        <v>30000</v>
+      </c>
+      <c r="E50">
+        <v>25000</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>14</v>
+      </c>
+      <c r="D51">
+        <v>10000</v>
+      </c>
+      <c r="E51">
+        <v>25000</v>
+      </c>
+      <c r="F51" t="b">
+        <v>1</v>
+      </c>
+      <c r="G51" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <v>15000</v>
+      </c>
+      <c r="E52">
+        <v>25000</v>
+      </c>
+      <c r="F52" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53">
+        <v>30000</v>
+      </c>
+      <c r="E53">
+        <v>25000</v>
+      </c>
+      <c r="F53" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54">
+        <v>10000</v>
+      </c>
+      <c r="E54">
+        <v>25000</v>
+      </c>
+      <c r="F54" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55">
+        <v>15000</v>
+      </c>
+      <c r="E55">
+        <v>25000</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56">
+        <v>30000</v>
+      </c>
+      <c r="E56">
+        <v>25000</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" t="s">
+        <v>13</v>
+      </c>
+      <c r="C57" t="s">
+        <v>14</v>
+      </c>
+      <c r="D57">
+        <v>10000</v>
+      </c>
+      <c r="E57">
+        <v>25000</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58">
+        <v>15000</v>
+      </c>
+      <c r="E58">
+        <v>25000</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59">
+        <v>30000</v>
+      </c>
+      <c r="E59">
+        <v>25000</v>
+      </c>
+      <c r="F59" t="b">
+        <v>1</v>
+      </c>
+      <c r="G59" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60">
+        <v>10000</v>
+      </c>
+      <c r="E60">
+        <v>25000</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" t="s">
+        <v>8</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61">
+        <v>15000</v>
+      </c>
+      <c r="E61">
+        <v>25000</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" t="s">
+        <v>9</v>
+      </c>
+      <c r="D62">
+        <v>30000</v>
+      </c>
+      <c r="E62">
+        <v>25000</v>
+      </c>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63" t="s">
+        <v>14</v>
+      </c>
+      <c r="D63">
+        <v>10000</v>
+      </c>
+      <c r="E63">
+        <v>25000</v>
+      </c>
+      <c r="F63" t="b">
+        <v>1</v>
+      </c>
+      <c r="G63" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64" t="s">
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64">
+        <v>15000</v>
+      </c>
+      <c r="E64">
+        <v>25000</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
+      </c>
+      <c r="D65">
+        <v>30000</v>
+      </c>
+      <c r="E65">
+        <v>25000</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66">
+        <v>10000</v>
+      </c>
+      <c r="E66">
+        <v>25000</v>
+      </c>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67">
+        <v>15000</v>
+      </c>
+      <c r="E67">
+        <v>25000</v>
+      </c>
+      <c r="F67" t="b">
+        <v>1</v>
+      </c>
+      <c r="G67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="s">
+        <v>8</v>
+      </c>
+      <c r="C68" t="s">
+        <v>9</v>
+      </c>
+      <c r="D68">
+        <v>30000</v>
+      </c>
+      <c r="E68">
+        <v>25000</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+      <c r="D69">
+        <v>10000</v>
+      </c>
+      <c r="E69">
+        <v>25000</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70">
+        <v>15000</v>
+      </c>
+      <c r="E70">
+        <v>25000</v>
+      </c>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="D71">
+        <v>30000</v>
+      </c>
+      <c r="E71">
+        <v>25000</v>
+      </c>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>14</v>
+      </c>
+      <c r="D72">
+        <v>10000</v>
+      </c>
+      <c r="E72">
+        <v>25000</v>
+      </c>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>13</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73">
+        <v>15000</v>
+      </c>
+      <c r="E73">
+        <v>25000</v>
+      </c>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="D74">
+        <v>30000</v>
+      </c>
+      <c r="E74">
+        <v>25000</v>
+      </c>
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75">
+        <v>10000</v>
+      </c>
+      <c r="E75">
+        <v>25000</v>
+      </c>
+      <c r="F75" t="b">
+        <v>1</v>
+      </c>
+      <c r="G75" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76">
+        <v>15000</v>
+      </c>
+      <c r="E76">
+        <v>25000</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" t="s">
+        <v>9</v>
+      </c>
+      <c r="D77">
+        <v>30000</v>
+      </c>
+      <c r="E77">
+        <v>25000</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78">
+        <v>10000</v>
+      </c>
+      <c r="E78">
+        <v>25000</v>
+      </c>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79">
+        <v>15000</v>
+      </c>
+      <c r="E79">
+        <v>25000</v>
+      </c>
+      <c r="F79" t="b">
+        <v>1</v>
+      </c>
+      <c r="G79" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80" t="s">
+        <v>9</v>
+      </c>
+      <c r="D80">
+        <v>30000</v>
+      </c>
+      <c r="E80">
+        <v>25000</v>
+      </c>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" t="s">
+        <v>14</v>
+      </c>
+      <c r="D81">
+        <v>10000</v>
+      </c>
+      <c r="E81">
+        <v>25000</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82">
+        <v>15000</v>
+      </c>
+      <c r="E82">
+        <v>25000</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D83">
+        <v>30000</v>
+      </c>
+      <c r="E83">
+        <v>25000</v>
+      </c>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="s">
+        <v>13</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
+      </c>
+      <c r="D84">
+        <v>10000</v>
+      </c>
+      <c r="E84">
+        <v>25000</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85">
+        <v>15000</v>
+      </c>
+      <c r="E85">
+        <v>25000</v>
+      </c>
+      <c r="F85" t="b">
+        <v>1</v>
+      </c>
+      <c r="G85" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>9</v>
+      </c>
+      <c r="D86">
+        <v>30000</v>
+      </c>
+      <c r="E86">
+        <v>25000</v>
+      </c>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87">
+        <v>10000</v>
+      </c>
+      <c r="E87">
+        <v>25000</v>
+      </c>
+      <c r="F87" t="b">
+        <v>1</v>
+      </c>
+      <c r="G87" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88">
+        <v>15000</v>
+      </c>
+      <c r="E88">
+        <v>25000</v>
+      </c>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89">
+        <v>30000</v>
+      </c>
+      <c r="E89">
+        <v>25000</v>
+      </c>
+      <c r="F89" t="b">
+        <v>1</v>
+      </c>
+      <c r="G89" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90">
+        <v>10000</v>
+      </c>
+      <c r="E90">
+        <v>25000</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91">
+        <v>15000</v>
+      </c>
+      <c r="E91">
+        <v>25000</v>
+      </c>
+      <c r="F91" t="b">
+        <v>1</v>
+      </c>
+      <c r="G91" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92">
+        <v>30000</v>
+      </c>
+      <c r="E92">
+        <v>25000</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93">
+        <v>10000</v>
+      </c>
+      <c r="E93">
+        <v>25000</v>
+      </c>
+      <c r="F93" t="b">
+        <v>1</v>
+      </c>
+      <c r="G93" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94">
+        <v>15000</v>
+      </c>
+      <c r="E94">
+        <v>25000</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95">
+        <v>30000</v>
+      </c>
+      <c r="E95">
+        <v>25000</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="s">
+        <v>12</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96">
+        <v>10000</v>
+      </c>
+      <c r="E96">
+        <v>25000</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97">
+        <v>15000</v>
+      </c>
+      <c r="E97">
+        <v>25000</v>
+      </c>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="s">
+        <v>8</v>
+      </c>
+      <c r="C98" t="s">
+        <v>9</v>
+      </c>
+      <c r="D98">
+        <v>30000</v>
+      </c>
+      <c r="E98">
+        <v>25000</v>
+      </c>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>12</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99">
+        <v>10000</v>
+      </c>
+      <c r="E99">
+        <v>25000</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100">
+        <v>15000</v>
+      </c>
+      <c r="E100">
+        <v>25000</v>
+      </c>
+      <c r="F100" t="b">
+        <v>1</v>
+      </c>
+      <c r="G100" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" t="s">
+        <v>9</v>
+      </c>
+      <c r="D101">
+        <v>30000</v>
+      </c>
+      <c r="E101">
+        <v>25000</v>
+      </c>
+      <c r="F101" t="b">
+        <v>1</v>
+      </c>
+      <c r="G101" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102" t="s">
+        <v>14</v>
+      </c>
+      <c r="D102">
+        <v>10000</v>
+      </c>
+      <c r="E102">
+        <v>25000</v>
+      </c>
+      <c r="F102" t="b">
+        <v>1</v>
+      </c>
+      <c r="G102" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103">
+        <v>15000</v>
+      </c>
+      <c r="E103">
+        <v>25000</v>
+      </c>
+      <c r="F103" t="b">
+        <v>1</v>
+      </c>
+      <c r="G103" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" t="s">
+        <v>9</v>
+      </c>
+      <c r="D104">
+        <v>30000</v>
+      </c>
+      <c r="E104">
+        <v>25000</v>
+      </c>
+      <c r="F104" t="b">
+        <v>1</v>
+      </c>
+      <c r="G104" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="s">
+        <v>12</v>
+      </c>
+      <c r="C105" t="s">
+        <v>14</v>
+      </c>
+      <c r="D105">
+        <v>10000</v>
+      </c>
+      <c r="E105">
+        <v>25000</v>
+      </c>
+      <c r="F105" t="b">
+        <v>1</v>
+      </c>
+      <c r="G105" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106">
+        <v>15000</v>
+      </c>
+      <c r="E106">
+        <v>25000</v>
+      </c>
+      <c r="F106" t="b">
+        <v>1</v>
+      </c>
+      <c r="G106" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" t="s">
+        <v>9</v>
+      </c>
+      <c r="D107">
+        <v>30000</v>
+      </c>
+      <c r="E107">
+        <v>25000</v>
+      </c>
+      <c r="F107" t="b">
+        <v>1</v>
+      </c>
+      <c r="G107" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>12</v>
+      </c>
+      <c r="C108" t="s">
+        <v>14</v>
+      </c>
+      <c r="D108">
+        <v>10000</v>
+      </c>
+      <c r="E108">
+        <v>25000</v>
+      </c>
+      <c r="F108" t="b">
+        <v>1</v>
+      </c>
+      <c r="G108" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109">
+        <v>15000</v>
+      </c>
+      <c r="E109">
+        <v>25000</v>
+      </c>
+      <c r="F109" t="b">
+        <v>1</v>
+      </c>
+      <c r="G109" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="s">
+        <v>12</v>
+      </c>
+      <c r="C110" t="s">
+        <v>9</v>
+      </c>
+      <c r="D110">
+        <v>30000</v>
+      </c>
+      <c r="E110">
+        <v>25000</v>
+      </c>
+      <c r="F110" t="b">
+        <v>1</v>
+      </c>
+      <c r="G110" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111">
+        <v>10000</v>
+      </c>
+      <c r="E111">
+        <v>25000</v>
+      </c>
+      <c r="F111" t="b">
+        <v>1</v>
+      </c>
+      <c r="G111" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112">
+        <v>15000</v>
+      </c>
+      <c r="E112">
+        <v>25000</v>
+      </c>
+      <c r="F112" t="b">
+        <v>1</v>
+      </c>
+      <c r="G112" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D113">
+        <v>30000</v>
+      </c>
+      <c r="E113">
+        <v>25000</v>
+      </c>
+      <c r="F113" t="b">
+        <v>1</v>
+      </c>
+      <c r="G113" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" t="s">
+        <v>14</v>
+      </c>
+      <c r="D114">
+        <v>10000</v>
+      </c>
+      <c r="E114">
+        <v>25000</v>
+      </c>
+      <c r="F114" t="b">
+        <v>1</v>
+      </c>
+      <c r="G114" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115">
+        <v>15000</v>
+      </c>
+      <c r="E115">
+        <v>25000</v>
+      </c>
+      <c r="F115" t="b">
+        <v>1</v>
+      </c>
+      <c r="G115" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="s">
+        <v>12</v>
+      </c>
+      <c r="C116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116">
+        <v>30000</v>
+      </c>
+      <c r="E116">
+        <v>25000</v>
+      </c>
+      <c r="F116" t="b">
+        <v>1</v>
+      </c>
+      <c r="G116" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="s">
+        <v>13</v>
+      </c>
+      <c r="C117" t="s">
+        <v>14</v>
+      </c>
+      <c r="D117">
+        <v>10000</v>
+      </c>
+      <c r="E117">
+        <v>25000</v>
+      </c>
+      <c r="F117" t="b">
+        <v>1</v>
+      </c>
+      <c r="G117" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118">
+        <v>15000</v>
+      </c>
+      <c r="E118">
+        <v>25000</v>
+      </c>
+      <c r="F118" t="b">
+        <v>1</v>
+      </c>
+      <c r="G118" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="s">
+        <v>12</v>
+      </c>
+      <c r="C119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D119">
+        <v>30000</v>
+      </c>
+      <c r="E119">
+        <v>25000</v>
+      </c>
+      <c r="F119" t="b">
+        <v>1</v>
+      </c>
+      <c r="G119" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="s">
+        <v>13</v>
+      </c>
+      <c r="C120" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120">
+        <v>10000</v>
+      </c>
+      <c r="E120">
+        <v>25000</v>
+      </c>
+      <c r="F120" t="b">
+        <v>1</v>
+      </c>
+      <c r="G120" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121">
+        <v>15000</v>
+      </c>
+      <c r="E121">
+        <v>25000</v>
+      </c>
+      <c r="F121" t="b">
+        <v>1</v>
+      </c>
+      <c r="G121" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
+    <ignoredError sqref="A1:H1 B2:H2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>